--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -753,7 +753,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D32"/>
+  <dimension ref="A1:D42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,97 +448,205 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
+          <t>zuzbQnCF</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>YZZcMwBs</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -548,7 +656,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -558,7 +666,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -568,7 +676,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -578,7 +686,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -588,7 +696,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -598,7 +706,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -608,7 +716,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -618,7 +726,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -628,7 +736,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -638,7 +746,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -648,7 +756,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -658,7 +766,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -668,7 +776,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -678,7 +786,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -688,7 +796,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -698,7 +806,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -708,7 +816,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -718,7 +826,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -728,7 +836,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -738,7 +846,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -748,22 +856,122 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
+          <t>tvOIPExA</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>W67CmLPh</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr"/>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>4.00</t>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>4.10</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,183 +470,87 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
+          <t>hIsO3XFj</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
+          <t>EF8gXauC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
+          <t>lONsG15D</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
+          <t>0K2qBFNG</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
+          <t>Kj4sifWp</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
+          <t>bF2q76Mr</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.25</t>
-        </is>
-      </c>
+          <t>vyk5gjdE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -656,7 +560,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -666,7 +570,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -676,7 +580,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -686,7 +590,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -696,7 +600,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -706,7 +610,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -716,7 +620,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -726,7 +630,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -736,7 +640,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -746,7 +650,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -756,7 +660,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -766,7 +670,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -776,7 +680,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -786,7 +690,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -796,7 +700,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -806,7 +710,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -816,7 +720,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -826,7 +730,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -836,7 +740,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -846,7 +750,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -856,7 +760,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -866,110 +770,20 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>W67CmLPh</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr"/>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>1.80</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>4.10</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,104 +453,200 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.60</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
+          <t>YZZcMwBs</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
       <c r="B11" t="inlineStr"/>
@@ -560,7 +656,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
       <c r="B12" t="inlineStr"/>
@@ -570,7 +666,7 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr"/>
@@ -580,7 +676,7 @@
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>lONsG15D</t>
         </is>
       </c>
       <c r="B14" t="inlineStr"/>
@@ -590,7 +686,7 @@
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr"/>
@@ -600,7 +696,7 @@
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
       <c r="B16" t="inlineStr"/>
@@ -610,7 +706,7 @@
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
       <c r="B17" t="inlineStr"/>
@@ -620,7 +716,7 @@
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr"/>
@@ -630,7 +726,7 @@
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr"/>
@@ -640,7 +736,7 @@
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -650,7 +746,7 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
@@ -660,7 +756,7 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
       <c r="B22" t="inlineStr"/>
@@ -670,7 +766,7 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
       <c r="B23" t="inlineStr"/>
@@ -680,7 +776,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -690,7 +786,7 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
@@ -700,7 +796,7 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
       <c r="B26" t="inlineStr"/>
@@ -710,7 +806,7 @@
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
       <c r="B27" t="inlineStr"/>
@@ -720,7 +816,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
       <c r="B28" t="inlineStr"/>
@@ -730,7 +826,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
       <c r="B29" t="inlineStr"/>
@@ -740,7 +836,7 @@
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr"/>
@@ -750,7 +846,7 @@
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
       <c r="B31" t="inlineStr"/>
@@ -760,7 +856,7 @@
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
       <c r="B32" t="inlineStr"/>
@@ -770,20 +866,100 @@
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr"/>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr"/>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr"/>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr"/>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>1.80</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D41" t="inlineStr">
         <is>
           <t>4.10</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -629,7 +629,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -646,137 +646,293 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>djSMofvg</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>U3QUqY85</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>QVJwrCwI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>34.00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>19.00</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>1.02</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
       <c r="B24" t="inlineStr"/>
@@ -786,184 +942,12 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>6u6i5pie</t>
         </is>
       </c>
       <c r="B25" t="inlineStr"/>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>6q2yrHgU</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AiJ3kset</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>t2AoZLAa</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>jFMCm08e</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>tvOIPExA</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D41"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>1.48</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -646,97 +646,205 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
+          <t>djSMofvg</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
+          <t>U3QUqY85</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
+          <t>QVJwrCwI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
       <c r="B20" t="inlineStr"/>
@@ -746,224 +854,12 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>6u6i5pie</t>
         </is>
       </c>
       <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>8QPARz8c</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr"/>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>hzyf0b9b</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>CpiTEcOi</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr"/>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>8CpxDyg4</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr"/>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>6q2yrHgU</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AiJ3kset</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr"/>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr"/>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>t2AoZLAa</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr"/>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>jFMCm08e</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr"/>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>tvOIPExA</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr"/>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr"/>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr"/>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr"/>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr"/>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr"/>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr"/>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr"/>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr"/>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.10</t>
         </is>
       </c>
     </row>
@@ -519,12 +519,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>8.50</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.30</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -705,7 +705,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -749,7 +749,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
@@ -827,12 +827,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -840,26 +840,6 @@
           <t>13.00</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>W67CmLPh</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr"/>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>6u6i5pie</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,34 +448,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zuzbQnCF</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>GbeXvnR8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,359 +485,95 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>O48oHrZ1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>2FREIeA6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>dfO6OQtS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>9.50</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>SxFxJ44k</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>8.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>SxFxJ44k</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>t0w6KHuf</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>AuVMGZvJ</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>djSMofvg</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>U3QUqY85</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>AgAeVYgC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>QVJwrCwI</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>61DvZGfm</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
           <t>4.33</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>0OYDmG9t</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>AVR8vwXP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>13.00</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,34 +448,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,95 +485,205 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.20</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>11.00</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,34 +448,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,41 +485,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,159 +529,115 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
         <is>
           <t>11.00</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.63</t>
         </is>
       </c>
     </row>
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>3.70</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
@@ -585,17 +585,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,12 +448,12 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,183 +463,315 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>3.10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
           <t>4.10</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1.80</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>11.00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.30</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,330 +448,44 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>QVJwrCwI</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>61DvZGfm</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>0OYDmG9t</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>AVR8vwXP</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
           <t>11.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>zsmd0ggn</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>UwsvBA74</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>vZqDdBhB</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>r7j4bXNb</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>WSMotj8U</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>tI0qkTpo</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>x4pn9lxH</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>8.50</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.30</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,44 +448,198 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>UwsvBA74</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.20</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8OhVCWxh</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.80</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,7 +453,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,7 +463,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.57</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
@@ -629,17 +629,215 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dCL13J5e</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pY1dP0SE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>1.62</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,396 +448,44 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zsmd0ggn</t>
+          <t>CnrLfkNN</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>UwsvBA74</t>
+          <t>8OhVCWxh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>vZqDdBhB</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>r7j4bXNb</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WSMotj8U</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tI0qkTpo</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>x4pn9lxH</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>6.25</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>CnrLfkNN</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
           <t>3.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>8OhVCWxh</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>dCL13J5e</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>pY1dP0SE</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>QNoNA1DL</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>hvFA1cz8</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>AeNg5uyq</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>IcrFCNr9</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Uy2KjtMk</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>2k0SlKj2</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dQ0zIIKl</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>1.62</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,12 +448,12 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>dCL13J5e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,29 +463,381 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>3.50</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3.20</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,12 +448,12 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dCL13J5e</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -463,19 +463,19 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>3.75</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pY1dP0SE</t>
+          <t>QNoNA1DL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -485,359 +485,139 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>2.50</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QNoNA1DL</t>
+          <t>hvFA1cz8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hvFA1cz8</t>
+          <t>AeNg5uyq</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>1.36</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AeNg5uyq</t>
+          <t>IcrFCNr9</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>IcrFCNr9</t>
+          <t>Uy2KjtMk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Uy2KjtMk</t>
+          <t>2k0SlKj2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2k0SlKj2</t>
+          <t>dQ0zIIKl</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>dQ0zIIKl</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>rsNyMnwK</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CIlrT3pm</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6uSGCr06</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>f18BYPMP</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Q5hiEzKD</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SfGPAMUI</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>IukqGdk1</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>pWnjRsFa</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>bFO8E4Vg</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>3.20</t>
+          <t>1.62</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,44 +448,396 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>rsNyMnwK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>11.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>CIlrT3pm</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.40</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
           <t>3.50</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UajsPCkT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>7.00</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,12 +458,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>9.00</t>
         </is>
       </c>
     </row>
@@ -480,12 +480,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
@@ -546,12 +546,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
@@ -568,7 +568,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -585,17 +585,17 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>4.20</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>4.10</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.73</t>
         </is>
       </c>
     </row>
@@ -629,215 +629,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>UajsPCkT</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
           <t>2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tbtaPLqC</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.09</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>10.00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>21.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ENOasf5c</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lpXDJjDj</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dnhZQYKG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zwD8uYZ9</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>0KbQSfj4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ShoJUGLi</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>nc8W6DTp</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>7.00</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,196 +448,42 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rsNyMnwK</t>
+          <t>pWnjRsFa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>1.73</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CIlrT3pm</t>
+          <t>bFO8E4Vg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>6uSGCr06</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>f18BYPMP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Q5hiEzKD</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>SfGPAMUI</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>IukqGdk1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>pWnjRsFa</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>bFO8E4Vg</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
         <is>
           <t>2.70</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,44 +448,330 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pWnjRsFa</t>
+          <t>UajsPCkT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bFO8E4Vg</t>
+          <t>tbtaPLqC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>1.09</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>21.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>2.40</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>2.70</t>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.83</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,330 +448,264 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UajsPCkT</t>
+          <t>0KbQSfj4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>1.70</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tbtaPLqC</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.09</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21.00</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ENOasf5c</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>8.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lpXDJjDj</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>8.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dnhZQYKG</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zwD8uYZ9</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>1.83</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>7.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>M93rhBJF</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Eq0zfXl3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>E7rNpTBk</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.83</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,264 +448,396 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>9.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>7.00</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>M93rhBJF</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>Eq0zfXl3</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>E7rNpTBk</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>2mcmYkSq</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.83</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>ELNeaSQr</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
           <t>3.30</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>3.40</t>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3.25</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>8.50</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.25</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -551,7 +551,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.83</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>11.00</t>
         </is>
       </c>
     </row>
@@ -771,7 +771,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>1.53</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.20</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -458,12 +458,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>9.00</t>
         </is>
       </c>
     </row>
@@ -475,17 +475,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
@@ -502,12 +502,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>6.50</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
@@ -546,12 +546,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
@@ -590,12 +590,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -629,12 +629,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -661,7 +661,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,396 +448,44 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>4.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>r3GGwC4M</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>M93rhBJF</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Eq0zfXl3</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>E7rNpTBk</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>2mcmYkSq</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>nBwH6AY8</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>rPiijklS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2.05</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>4E8uaJWa</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>x0haJmIE</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ELNeaSQr</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Mku6FvHt</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
           <t>3.40</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>rwXP4l3L</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>MiACepQ7</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>WQadeyWO</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>9.00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>8.00</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>1.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ABBmcc1C</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.30</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>zyC4c6ee</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>3.25</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,44 +448,396 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
+          <t>x0haJmIE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ELNeaSQr</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>9.50</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.53</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>13.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>7.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>3.25</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>2.88</t>
         </is>
       </c>
     </row>
@@ -485,7 +485,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.91</t>
         </is>
       </c>
     </row>
@@ -497,17 +497,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
@@ -546,12 +546,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>9.50</t>
         </is>
       </c>
     </row>
@@ -563,12 +563,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>5.25</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>5.00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>5.25</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>12.00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
@@ -629,215 +629,17 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>3.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IHYEDIog</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>1.53</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>jVWMBdG5</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>13.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>485V7EFU</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>7.50</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8MVuSH0n</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2q7yHiho</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>AoSdOZaB</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>dr2N9zoI</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>GnZmQeVb</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>raQ4MDUN</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>3.25</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,198 +448,396 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4E8uaJWa</t>
+          <t>IHYEDIog</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>x0haJmIE</t>
+          <t>jVWMBdG5</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>13.00</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ELNeaSQr</t>
+          <t>485V7EFU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>5.50</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Mku6FvHt</t>
+          <t>8MVuSH0n</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>rwXP4l3L</t>
+          <t>2q7yHiho</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>2.75</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>2.45</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>MiACepQ7</t>
+          <t>AoSdOZaB</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>WQadeyWO</t>
+          <t>dr2N9zoI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12.00</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>9.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ABBmcc1C</t>
+          <t>GnZmQeVb</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>zyC4c6ee</t>
+          <t>raQ4MDUN</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>v3DAZKP9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>biQrHC9r</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6.50</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>nee3ysec</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6HTjFjve</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>11.00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YmumZjET</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>j5mWxZE4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>UJQITUyi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>UkaNveph</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xMovyDqH</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>3.50</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>3.10</t>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.55</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,17 +453,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
@@ -480,7 +480,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -502,7 +502,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -519,7 +519,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
@@ -541,12 +541,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -563,12 +563,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
@@ -629,7 +629,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -640,204 +640,6 @@
       <c r="D10" t="inlineStr">
         <is>
           <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>v3DAZKP9</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2.40</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>biQrHC9r</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>7.00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>nee3ysec</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>6HTjFjve</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>11.00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>1.25</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YmumZjET</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>j5mWxZE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>UJQITUyi</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UkaNveph</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1.80</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>3.80</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xMovyDqH</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>2.55</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -448,198 +448,198 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IHYEDIog</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jVWMBdG5</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>8.00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13.00</t>
+          <t>1.27</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>485V7EFU</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8MVuSH0n</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>11.00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>5.75</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.27</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2q7yHiho</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AoSdOZaB</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dr2N9zoI</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.20</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>GnZmQeVb</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>raQ4MDUN</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next_odds.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -458,12 +458,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
@@ -475,17 +475,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7.00</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.25</t>
         </is>
       </c>
     </row>
@@ -497,7 +497,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -507,7 +507,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -519,17 +519,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.00</t>
+          <t>9.50</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.75</t>
+          <t>7.50</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.22</t>
         </is>
       </c>
     </row>
@@ -541,17 +541,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
@@ -563,17 +563,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -595,7 +595,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
@@ -607,17 +607,17 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
@@ -629,17 +629,171 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>2.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EuQnZBVQ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>10.00</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2qNaDU87</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>15.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOGITkgl</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>E38ZP7hD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>fwAoyY0E</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SrjMmBpK</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6w5RRTN0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>4.75</t>
         </is>
       </c>
     </row>
